--- a/data/trans_orig/RUIDO_2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan el ruido en su municipio o lugar de residencia en 2023</t>
+          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan el ruido en su municipio o lugar de residencia en 2023 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25483</t>
+          <t>23597</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,47 +745,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,8%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1129</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3648</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1129</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3504</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24996</t>
+          <t>27695</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13482</t>
+          <t>13390</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30039</t>
+          <t>28635</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42013</t>
+          <t>41817</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60503</t>
+          <t>60330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57557</t>
+          <t>57715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83613</t>
+          <t>84068</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54776</t>
+          <t>55159</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80523</t>
+          <t>79134</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56230</t>
+          <t>55450</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>75080</t>
+          <t>74798</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118243</t>
+          <t>118880</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>148305</t>
+          <t>150153</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,86%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32046</t>
+          <t>31279</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18167</t>
+          <t>18091</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24571</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46068</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16201</t>
+          <t>15429</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12305</t>
+          <t>11835</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26125</t>
+          <t>25820</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25785</t>
+          <t>25287</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57384</t>
+          <t>57729</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32823</t>
+          <t>33266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53007</t>
+          <t>53192</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64835</t>
+          <t>63183</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104442</t>
+          <t>100528</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64733</t>
+          <t>65412</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98279</t>
+          <t>100301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72496</t>
+          <t>71248</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94792</t>
+          <t>94711</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145331</t>
+          <t>145576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>187155</t>
+          <t>187863</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>48,06%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56311</t>
+          <t>54355</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89407</t>
+          <t>87793</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33752</t>
+          <t>33857</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52603</t>
+          <t>53319</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>95136</t>
+          <t>95190</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>131959</t>
+          <t>131543</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10666</t>
+          <t>11264</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18518</t>
+          <t>18058</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22924</t>
+          <t>24230</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18529</t>
+          <t>18882</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13582</t>
+          <t>14168</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39379</t>
+          <t>36920</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15763</t>
+          <t>14891</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>11700</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25626</t>
+          <t>26208</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32063</t>
+          <t>32387</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52338</t>
+          <t>51753</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42861</t>
+          <t>43677</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60858</t>
+          <t>62443</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78961</t>
+          <t>80651</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>106892</t>
+          <t>107567</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,76%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48925</t>
+          <t>48422</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71455</t>
+          <t>71914</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38434</t>
+          <t>37439</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54923</t>
+          <t>54153</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>91588</t>
+          <t>90495</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>120224</t>
+          <t>120791</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16863</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16690</t>
+          <t>16561</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13871</t>
+          <t>13238</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28498</t>
+          <t>29041</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15381</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31168</t>
+          <t>30553</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>13367</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26996</t>
+          <t>25532</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32064</t>
+          <t>31423</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51975</t>
+          <t>50931</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22205</t>
+          <t>21651</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53776</t>
+          <t>54966</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32288</t>
+          <t>32469</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52345</t>
+          <t>52284</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57686</t>
+          <t>59233</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96043</t>
+          <t>95935</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13396</t>
+          <t>13597</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34221</t>
+          <t>33519</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24932</t>
+          <t>25794</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47650</t>
+          <t>47441</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>42666</t>
+          <t>42812</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>73740</t>
+          <t>71958</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21944</t>
+          <t>22047</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47395</t>
+          <t>46679</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16287</t>
+          <t>15395</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30531</t>
+          <t>30765</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>42404</t>
+          <t>41681</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>72633</t>
+          <t>70579</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14683</t>
+          <t>14672</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16837</t>
+          <t>17719</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22338</t>
+          <t>22184</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44191</t>
+          <t>44966</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32651</t>
+          <t>33090</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>52515</t>
+          <t>51501</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>60154</t>
+          <t>60363</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>90090</t>
+          <t>88900</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>384</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15862</t>
+          <t>15796</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18853</t>
+          <t>19081</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29290</t>
+          <t>29468</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28161</t>
+          <t>28389</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>42092</t>
+          <t>42532</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>24345</t>
+          <t>24162</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34450</t>
+          <t>34306</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31429</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>42392</t>
+          <t>42192</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>59155</t>
+          <t>59234</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>73854</t>
+          <t>73781</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,44%</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,62 +3832,62 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>3975</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>1296</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>4773</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>523</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>859</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>538</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10192</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>27802</t>
+          <t>26747</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>44651</t>
+          <t>44725</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>31254</t>
+          <t>31525</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>46814</t>
+          <t>46935</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>61932</t>
+          <t>61002</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>87174</t>
+          <t>86268</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,8%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>43550</t>
+          <t>45117</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>63177</t>
+          <t>64373</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>45480</t>
+          <t>46187</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>62221</t>
+          <t>63071</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>95794</t>
+          <t>96442</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>122818</t>
+          <t>122662</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,75%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>9637</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9457</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>22258</t>
+          <t>22899</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>21306</t>
+          <t>21025</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>21534</t>
+          <t>21690</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>39513</t>
+          <t>38966</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>20145</t>
+          <t>21046</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>52676</t>
+          <t>54416</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>50770</t>
+          <t>52164</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>21071</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>93879</t>
+          <t>96099</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>23009</t>
+          <t>23558</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>45660</t>
+          <t>46608</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>90887</t>
+          <t>89178</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>364127</t>
+          <t>362970</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>114645</t>
+          <t>113463</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>495880</t>
+          <t>466150</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>74,4%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>81653</t>
+          <t>81978</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>119367</t>
+          <t>118153</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>189599</t>
+          <t>189851</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>78393</t>
+          <t>90943</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>296288</t>
+          <t>294540</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,01%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>16651</t>
+          <t>17256</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>38267</t>
+          <t>39892</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>63866</t>
+          <t>64274</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>20407</t>
+          <t>23308</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>88662</t>
+          <t>89593</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>30538</t>
+          <t>30658</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>34494</t>
+          <t>34396</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>12181</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>58260</t>
+          <t>58731</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9165</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>155</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>849</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>10449</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>28884</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>55207</t>
+          <t>53239</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>43956</t>
+          <t>44153</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>67620</t>
+          <t>69213</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>80190</t>
+          <t>78944</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>113876</t>
+          <t>113263</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>61860</t>
+          <t>61485</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>91159</t>
+          <t>90254</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>58023</t>
+          <t>59186</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>82102</t>
+          <t>81855</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>127994</t>
+          <t>126570</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>165203</t>
+          <t>164216</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>99061</t>
+          <t>99253</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>131062</t>
+          <t>131080</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>89483</t>
+          <t>87746</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>116165</t>
+          <t>115976</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>194438</t>
+          <t>196312</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>240714</t>
+          <t>238141</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>37755</t>
+          <t>37739</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>59835</t>
+          <t>61612</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>57051</t>
+          <t>56707</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>81903</t>
+          <t>81416</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>101307</t>
+          <t>101682</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>135688</t>
+          <t>136104</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>99971</t>
+          <t>100104</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>163995</t>
+          <t>167002</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>75302</t>
+          <t>72979</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>149638</t>
+          <t>151828</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>195872</t>
+          <t>195522</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>296553</t>
+          <t>296322</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>248583</t>
+          <t>252177</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>313491</t>
+          <t>317602</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>440661</t>
+          <t>439397</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>913501</t>
+          <t>890283</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>710318</t>
+          <t>709346</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1333496</t>
+          <t>1353989</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>450314</t>
+          <t>452150</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>527014</t>
+          <t>531702</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>282932</t>
+          <t>278057</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>508186</t>
+          <t>506462</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>702130</t>
+          <t>692803</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1014349</t>
+          <t>1011986</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>159317</t>
+          <t>160164</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>211053</t>
+          <t>212122</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>111439</t>
+          <t>111466</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>208890</t>
+          <t>212570</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>270599</t>
+          <t>278263</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>400077</t>
+          <t>401916</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>133150</t>
+          <t>135529</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>182691</t>
+          <t>184790</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>112928</t>
+          <t>120102</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>219008</t>
+          <t>219843</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>264235</t>
+          <t>260708</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>379795</t>
+          <t>384272</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>846</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23597</t>
+          <t>14217</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>460</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27695</t>
+          <t>16791</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19630</t>
+          <t>36411</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13390</t>
+          <t>26979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28635</t>
+          <t>47327</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50450</t>
+          <t>62037</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41817</t>
+          <t>50857</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60330</t>
+          <t>72868</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>70080</t>
+          <t>98448</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57715</t>
+          <t>82572</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84068</t>
+          <t>112953</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>39,35%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>68162</t>
+          <t>66950</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55159</t>
+          <t>55209</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79134</t>
+          <t>78840</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65799</t>
+          <t>67082</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55450</t>
+          <t>57006</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74798</t>
+          <t>76984</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>133961</t>
+          <t>134032</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118880</t>
+          <t>118901</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>150153</t>
+          <t>149453</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>52,07%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>18556</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13376</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31279</t>
+          <t>27524</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12562</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18091</t>
+          <t>17742</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>30663</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24496</t>
+          <t>21962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>40600</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9708</t>
+          <t>9484</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15429</t>
+          <t>15616</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>13300</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>18304</t>
+          <t>17953</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11835</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25820</t>
+          <t>25155</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>125527</t>
+          <t>135857</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>125527</t>
+          <t>135857</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125527</t>
+          <t>135857</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>138536</t>
+          <t>151180</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>138536</t>
+          <t>151180</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>138536</t>
+          <t>151180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>264063</t>
+          <t>287037</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>264063</t>
+          <t>287037</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>264063</t>
+          <t>287037</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39245</t>
+          <t>37713</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25287</t>
+          <t>24699</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57729</t>
+          <t>55746</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42686</t>
+          <t>45965</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33266</t>
+          <t>36139</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53192</t>
+          <t>57515</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>81931</t>
+          <t>83678</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63183</t>
+          <t>67901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100528</t>
+          <t>103125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81933</t>
+          <t>83281</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65412</t>
+          <t>65686</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100301</t>
+          <t>100465</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82999</t>
+          <t>90174</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71248</t>
+          <t>77235</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94711</t>
+          <t>101470</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>164932</t>
+          <t>173455</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145576</t>
+          <t>154459</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>187863</t>
+          <t>195357</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,48%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>70328</t>
+          <t>70970</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54355</t>
+          <t>56106</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87793</t>
+          <t>88603</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>42367</t>
+          <t>42058</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33857</t>
+          <t>32693</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53319</t>
+          <t>52280</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112695</t>
+          <t>113028</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>95190</t>
+          <t>94461</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>131543</t>
+          <t>133343</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9555</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18058</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24230</t>
+          <t>22218</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12090</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18882</t>
+          <t>19274</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>21768</t>
+          <t>22698</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14168</t>
+          <t>13860</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36920</t>
+          <t>34988</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>204526</t>
+          <t>205726</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>204526</t>
+          <t>205726</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>204526</t>
+          <t>205726</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>186355</t>
+          <t>197245</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>186355</t>
+          <t>197245</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>186355</t>
+          <t>197245</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>390881</t>
+          <t>402971</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>390881</t>
+          <t>402971</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>390881</t>
+          <t>402971</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14891</t>
+          <t>14895</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14716</t>
+          <t>14190</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>17244</t>
+          <t>16752</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26208</t>
+          <t>24421</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41303</t>
+          <t>42615</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32387</t>
+          <t>32599</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51753</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>52021</t>
+          <t>54914</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43677</t>
+          <t>45540</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62443</t>
+          <t>64360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>93324</t>
+          <t>97528</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>80651</t>
+          <t>84309</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>107567</t>
+          <t>112229</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>39,04%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>59777</t>
+          <t>62279</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48422</t>
+          <t>50408</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71914</t>
+          <t>74611</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>45888</t>
+          <t>47200</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37439</t>
+          <t>39003</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54153</t>
+          <t>56492</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>105664</t>
+          <t>109478</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>90495</t>
+          <t>96377</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>120791</t>
+          <t>125415</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16575</t>
+          <t>16254</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10451</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16561</t>
+          <t>16852</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>20558</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13238</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29041</t>
+          <t>29022</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>21443</t>
+          <t>22296</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14775</t>
+          <t>15424</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30553</t>
+          <t>30646</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>19322</t>
+          <t>20852</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13367</t>
+          <t>14708</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25532</t>
+          <t>28374</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>40765</t>
+          <t>43149</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31423</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50931</t>
+          <t>54643</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>140962</t>
+          <t>145205</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>140962</t>
+          <t>145205</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>140962</t>
+          <t>145205</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>136593</t>
+          <t>142257</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>136593</t>
+          <t>142257</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>136593</t>
+          <t>142257</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>277555</t>
+          <t>287462</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>277555</t>
+          <t>287462</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>277555</t>
+          <t>287462</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>32946</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21651</t>
+          <t>20984</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54966</t>
+          <t>51122</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>40879</t>
+          <t>44156</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32469</t>
+          <t>33669</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52284</t>
+          <t>57827</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>74031</t>
+          <t>77102</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59233</t>
+          <t>61676</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95935</t>
+          <t>99682</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>21735</t>
+          <t>31676</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13597</t>
+          <t>20882</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33519</t>
+          <t>47039</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>34673</t>
+          <t>40400</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25794</t>
+          <t>29348</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47441</t>
+          <t>53235</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>56408</t>
+          <t>72076</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>42812</t>
+          <t>56769</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>71958</t>
+          <t>90924</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33042</t>
+          <t>41040</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22047</t>
+          <t>26993</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46679</t>
+          <t>56148</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22533</t>
+          <t>25167</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15395</t>
+          <t>18781</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30765</t>
+          <t>34880</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>55574</t>
+          <t>66207</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>41681</t>
+          <t>50174</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>70579</t>
+          <t>83583</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -3110,27 +3110,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>636</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14672</t>
+          <t>15253</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17719</t>
+          <t>20180</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>32029</t>
+          <t>34391</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22184</t>
+          <t>23728</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44966</t>
+          <t>47986</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>42131</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33090</t>
+          <t>39439</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51501</t>
+          <t>63218</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>74160</t>
+          <t>84082</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>60363</t>
+          <t>67449</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>88900</t>
+          <t>101013</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,53%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>121969</t>
+          <t>142671</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>121969</t>
+          <t>142671</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>121969</t>
+          <t>142671</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>147857</t>
+          <t>167872</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>147857</t>
+          <t>167872</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>147857</t>
+          <t>167872</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>269826</t>
+          <t>310543</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>269826</t>
+          <t>310543</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>269826</t>
+          <t>310543</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,22 +3488,22 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>410</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>809</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>10562</t>
+          <t>12099</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15796</t>
+          <t>18398</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>23972</t>
+          <t>25675</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>19845</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29468</t>
+          <t>31411</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>34534</t>
+          <t>37774</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28389</t>
+          <t>30317</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>42532</t>
+          <t>45506</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>29826</t>
+          <t>33348</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>24162</t>
+          <t>26462</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34306</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>36961</t>
+          <t>39846</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>30819</t>
+          <t>33534</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>42192</t>
+          <t>45307</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>66787</t>
+          <t>73193</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>59234</t>
+          <t>64380</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>73781</t>
+          <t>80716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,56%</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4337</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>867</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,22 +3975,22 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>569</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>44145</t>
+          <t>49414</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>44145</t>
+          <t>49414</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>44145</t>
+          <t>49414</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>63660</t>
+          <t>68325</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>63660</t>
+          <t>68325</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>63660</t>
+          <t>68325</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>107804</t>
+          <t>117738</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>107804</t>
+          <t>117738</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>107804</t>
+          <t>117738</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>740</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7925</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,22 +4170,22 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>551</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>35451</t>
+          <t>37980</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>26747</t>
+          <t>29839</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>44725</t>
+          <t>48187</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>40598</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>31525</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>46935</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>73921</t>
+          <t>78578</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>61002</t>
+          <t>66861</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>86268</t>
+          <t>90513</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>39,17%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>54325</t>
+          <t>52385</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>45117</t>
+          <t>42442</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>64373</t>
+          <t>61741</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>54267</t>
+          <t>55139</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>46187</t>
+          <t>46071</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>63071</t>
+          <t>64089</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>108592</t>
+          <t>107524</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>96442</t>
+          <t>94299</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>122662</t>
+          <t>120651</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9473</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>14744</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>22899</t>
+          <t>21635</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>14876</t>
+          <t>14799</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>10169</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>21025</t>
+          <t>20644</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>29620</t>
+          <t>28990</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>21690</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>38966</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>112848</t>
+          <t>112693</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>112848</t>
+          <t>112693</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>112848</t>
+          <t>112693</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>115380</t>
+          <t>118393</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>115380</t>
+          <t>118393</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>115380</t>
+          <t>118393</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>228227</t>
+          <t>231087</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>228227</t>
+          <t>231087</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>228227</t>
+          <t>231087</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>34628</t>
+          <t>38261</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>21046</t>
+          <t>22869</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>54416</t>
+          <t>56459</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>22901</t>
+          <t>30121</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>21987</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>52164</t>
+          <t>42463</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>57529</t>
+          <t>68382</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>50016</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>96099</t>
+          <t>90514</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>32700</t>
+          <t>38070</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>23558</t>
+          <t>27147</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>46608</t>
+          <t>51400</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>254847</t>
+          <t>62199</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>89178</t>
+          <t>50968</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>362970</t>
+          <t>75054</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>287547</t>
+          <t>100268</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>113463</t>
+          <t>84855</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>466150</t>
+          <t>118537</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>98192</t>
+          <t>105460</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>81978</t>
+          <t>89337</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>118153</t>
+          <t>125067</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>92540</t>
+          <t>108273</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>28081</t>
+          <t>95343</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>189851</t>
+          <t>123650</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>190732</t>
+          <t>213733</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>90943</t>
+          <t>189917</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>294540</t>
+          <t>235430</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>48,27%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>26131</t>
+          <t>28114</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>39892</t>
+          <t>41349</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>29216</t>
+          <t>32246</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>23526</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>64274</t>
+          <t>43988</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>55347</t>
+          <t>60360</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>23308</t>
+          <t>47279</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>89593</t>
+          <t>76985</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>24642</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>12143</t>
+          <t>15752</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>30658</t>
+          <t>36570</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>15442</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>34396</t>
+          <t>28439</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>35381</t>
+          <t>44964</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>14977</t>
+          <t>34626</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>58731</t>
+          <t>60071</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>211591</t>
+          <t>234546</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>211591</t>
+          <t>234546</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>211591</t>
+          <t>234546</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>414945</t>
+          <t>253161</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>414945</t>
+          <t>253161</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>414945</t>
+          <t>253161</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>626536</t>
+          <t>487707</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>626536</t>
+          <t>487707</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>626536</t>
+          <t>487707</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>10094</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>13094</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>40029</t>
+          <t>51016</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>28884</t>
+          <t>37253</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>53239</t>
+          <t>66724</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>55574</t>
+          <t>67846</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>44153</t>
+          <t>53995</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>69213</t>
+          <t>83959</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>95603</t>
+          <t>118862</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>78944</t>
+          <t>100747</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>113263</t>
+          <t>143858</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>74724</t>
+          <t>85490</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>61485</t>
+          <t>69184</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>90254</t>
+          <t>102639</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>70381</t>
+          <t>80197</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>59186</t>
+          <t>66216</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>81855</t>
+          <t>93661</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>145105</t>
+          <t>165687</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>126570</t>
+          <t>145113</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>164216</t>
+          <t>187207</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>114344</t>
+          <t>133825</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>99253</t>
+          <t>115275</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>131080</t>
+          <t>152412</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>101991</t>
+          <t>115388</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>87746</t>
+          <t>100224</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>115976</t>
+          <t>131406</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>216335</t>
+          <t>249213</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>196312</t>
+          <t>225153</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>238141</t>
+          <t>276047</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>40,88%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>48304</t>
+          <t>57668</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>37739</t>
+          <t>46386</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>61612</t>
+          <t>73584</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>68878</t>
+          <t>79194</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>56707</t>
+          <t>66149</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>81416</t>
+          <t>94420</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>117183</t>
+          <t>136862</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>101682</t>
+          <t>117920</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>136104</t>
+          <t>158394</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>280082</t>
+          <t>330985</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>280082</t>
+          <t>330985</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>280082</t>
+          <t>330985</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>297689</t>
+          <t>344357</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>297689</t>
+          <t>344357</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>297689</t>
+          <t>344357</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>577771</t>
+          <t>675342</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>577771</t>
+          <t>675342</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>577771</t>
+          <t>675342</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>128454</t>
+          <t>128215</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>100104</t>
+          <t>102008</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>167002</t>
+          <t>162206</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,32 +6216,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>121541</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>72979</t>
+          <t>116416</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>151828</t>
+          <t>158367</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>249995</t>
+          <t>264735</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>195522</t>
+          <t>232760</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>296322</t>
+          <t>303362</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>283343</t>
+          <t>333148</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>252177</t>
+          <t>301118</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>317602</t>
+          <t>368133</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>593006</t>
+          <t>443842</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>439397</t>
+          <t>412819</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>890283</t>
+          <t>477928</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>876349</t>
+          <t>776990</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>709346</t>
+          <t>731268</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1353989</t>
+          <t>823405</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>488377</t>
+          <t>517923</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>452150</t>
+          <t>481749</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>531702</t>
+          <t>558061</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>430735</t>
+          <t>464961</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>278057</t>
+          <t>432223</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>506462</t>
+          <t>494134</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>919112</t>
+          <t>982883</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>692803</t>
+          <t>933651</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1011986</t>
+          <t>1032145</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>184430</t>
+          <t>203344</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>160164</t>
+          <t>176116</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>212122</t>
+          <t>234296</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>173576</t>
+          <t>191067</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>111466</t>
+          <t>169281</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>212570</t>
+          <t>214024</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>358005</t>
+          <t>394411</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>278263</t>
+          <t>364463</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>401916</t>
+          <t>433554</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>157048</t>
+          <t>174468</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>135529</t>
+          <t>152101</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>184790</t>
+          <t>205744</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>182156</t>
+          <t>206400</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>120102</t>
+          <t>185126</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>219843</t>
+          <t>230343</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>339203</t>
+          <t>380868</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>260708</t>
+          <t>351474</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>384272</t>
+          <t>417216</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>1241651</t>
+          <t>1357099</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1241651</t>
+          <t>1357099</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1241651</t>
+          <t>1357099</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>1501014</t>
+          <t>1442790</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>1501014</t>
+          <t>1442790</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>1501014</t>
+          <t>1442790</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>2742665</t>
+          <t>2799888</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>2742665</t>
+          <t>2799888</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>2742665</t>
+          <t>2799888</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
